--- a/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/BULON CABEZA HEXAGONAL DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/BULON CABEZA HEXAGONAL DISMAY.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="16" customWidth="1" style="17" min="1" max="1"/>
@@ -712,14 +712,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="n">
-        <v>45211.54076875475</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -741,8 +737,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="17">
       <c r="A11" s="18" t="inlineStr">
         <is>
@@ -757,8 +751,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24.75" customHeight="1" s="17">
       <c r="A15" s="20" t="inlineStr">
         <is>
@@ -766,8 +758,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="18" customHeight="1" s="17">
       <c r="A18" s="7" t="inlineStr">
         <is>
@@ -800,7 +790,7 @@
       </c>
       <c r="C19" s="14" t="n"/>
       <c r="D19" s="6" t="n">
-        <v>1150.65</v>
+        <v>1085.526</v>
       </c>
       <c r="E19" s="10" t="n"/>
     </row>
@@ -817,7 +807,7 @@
       </c>
       <c r="C20" s="14" t="n"/>
       <c r="D20" s="6" t="n">
-        <v>1260.5</v>
+        <v>1189.151</v>
       </c>
       <c r="E20" s="2" t="n"/>
     </row>
@@ -834,7 +824,7 @@
       </c>
       <c r="C21" s="14" t="n"/>
       <c r="D21" s="6" t="n">
-        <v>1305.15</v>
+        <v>1231.274</v>
       </c>
       <c r="E21" s="2" t="n"/>
     </row>
@@ -851,7 +841,7 @@
       </c>
       <c r="C22" s="14" t="n"/>
       <c r="D22" s="6" t="n">
-        <v>1359.87</v>
+        <v>1282.898</v>
       </c>
       <c r="E22" s="2" t="n"/>
     </row>
@@ -868,7 +858,7 @@
       </c>
       <c r="C23" s="14" t="n"/>
       <c r="D23" s="6" t="n">
-        <v>1375.87</v>
+        <v>1500</v>
       </c>
       <c r="E23" s="2" t="n"/>
     </row>
@@ -885,7 +875,7 @@
       </c>
       <c r="C24" s="14" t="n"/>
       <c r="D24" s="6" t="n">
-        <v>1794.38</v>
+        <v>1692.817</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="17">
@@ -901,7 +891,7 @@
       </c>
       <c r="C25" s="14" t="n"/>
       <c r="D25" s="6" t="n">
-        <v>2021.7</v>
+        <v>1907.264</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="17">
@@ -917,7 +907,7 @@
       </c>
       <c r="C26" s="14" t="n"/>
       <c r="D26" s="6" t="n">
-        <v>2409.94</v>
+        <v>2273.531</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="17">
@@ -933,7 +923,7 @@
       </c>
       <c r="C27" s="14" t="n"/>
       <c r="D27" s="6" t="n">
-        <v>2709.27</v>
+        <v>2555.924</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="17">
@@ -949,7 +939,7 @@
       </c>
       <c r="C28" s="14" t="n"/>
       <c r="D28" s="6" t="n">
-        <v>2949.06</v>
+        <v>2782.138</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="17">
@@ -965,7 +955,7 @@
       </c>
       <c r="C29" s="14" t="n"/>
       <c r="D29" s="6" t="n">
-        <v>3222.64</v>
+        <v>3040.231</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="17">
@@ -981,7 +971,7 @@
       </c>
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="6" t="n">
-        <v>3572.67</v>
+        <v>3370.451</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="17">
@@ -997,7 +987,7 @@
       </c>
       <c r="C31" s="14" t="n"/>
       <c r="D31" s="6" t="n">
-        <v>3862.35</v>
+        <v>3643.731</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="17">
@@ -1013,7 +1003,7 @@
       </c>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="6" t="n">
-        <v>4047.42</v>
+        <v>3818.321</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="17">
@@ -1029,7 +1019,7 @@
       </c>
       <c r="C33" s="14" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>4598.61</v>
+        <v>4338.318</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="17">
@@ -1045,7 +1035,7 @@
       </c>
       <c r="C34" s="14" t="n"/>
       <c r="D34" s="6" t="n">
-        <v>1440.18</v>
+        <v>1358.666</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="17">
@@ -1061,7 +1051,7 @@
       </c>
       <c r="C35" s="14" t="n"/>
       <c r="D35" s="6" t="n">
-        <v>5061.28</v>
+        <v>4774.798</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="17">
@@ -1077,7 +1067,7 @@
       </c>
       <c r="C36" s="14" t="n"/>
       <c r="D36" s="6" t="n">
-        <v>5672.82</v>
+        <v>5351.722</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="17">
@@ -1093,7 +1083,7 @@
       </c>
       <c r="C37" s="14" t="n"/>
       <c r="D37" s="6" t="n">
-        <v>6075.15</v>
+        <v>5731.278</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="17"/>
@@ -1104,8 +1094,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="18" customHeight="1" s="17">
       <c r="A42" s="7" t="inlineStr">
         <is>
@@ -1137,7 +1125,7 @@
       </c>
       <c r="C43" s="14" t="n"/>
       <c r="D43" s="6" t="n">
-        <v>1837.07</v>
+        <v>1733.087</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="17">
@@ -1153,7 +1141,7 @@
       </c>
       <c r="C44" s="14" t="n"/>
       <c r="D44" s="6" t="n">
-        <v>1975.43</v>
+        <v>1863.615</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="17">
@@ -1169,7 +1157,7 @@
       </c>
       <c r="C45" s="14" t="n"/>
       <c r="D45" s="6" t="n">
-        <v>2008.42</v>
+        <v>1894.741</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="17">
@@ -1185,7 +1173,7 @@
       </c>
       <c r="C46" s="14" t="n"/>
       <c r="D46" s="6" t="n">
-        <v>2132.33</v>
+        <v>2011.638</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="17">
@@ -1201,7 +1189,7 @@
       </c>
       <c r="C47" s="14" t="n"/>
       <c r="D47" s="6" t="n">
-        <v>2337.52</v>
+        <v>2205.21</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" s="17">
@@ -1217,7 +1205,7 @@
       </c>
       <c r="C48" s="14" t="n"/>
       <c r="D48" s="6" t="n">
-        <v>2615.13</v>
+        <v>2467.106</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="17">
@@ -1233,7 +1221,7 @@
       </c>
       <c r="C49" s="14" t="n"/>
       <c r="D49" s="6" t="n">
-        <v>3130.11</v>
+        <v>2952.936</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="17">
@@ -1249,7 +1237,7 @@
       </c>
       <c r="C50" s="14" t="n"/>
       <c r="D50" s="6" t="n">
-        <v>3641.06</v>
+        <v>3434.97</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="17">
@@ -1265,7 +1253,7 @@
       </c>
       <c r="C51" s="14" t="n"/>
       <c r="D51" s="6" t="n">
-        <v>4047.42</v>
+        <v>3818.321</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="17">
@@ -1281,7 +1269,7 @@
       </c>
       <c r="C52" s="14" t="n"/>
       <c r="D52" s="6" t="n">
-        <v>4461.82</v>
+        <v>4209.266</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="17">
@@ -1297,7 +1285,7 @@
       </c>
       <c r="C53" s="14" t="n"/>
       <c r="D53" s="6" t="n">
-        <v>4968.75</v>
+        <v>4687.502</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="17">
@@ -1313,7 +1301,7 @@
       </c>
       <c r="C54" s="14" t="n"/>
       <c r="D54" s="6" t="n">
-        <v>5749.26</v>
+        <v>5423.838</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="17">
@@ -1329,7 +1317,7 @@
       </c>
       <c r="C55" s="14" t="n"/>
       <c r="D55" s="6" t="n">
-        <v>6115.38</v>
+        <v>5769.234</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="17">
@@ -1345,7 +1333,7 @@
       </c>
       <c r="C56" s="14" t="n"/>
       <c r="D56" s="6" t="n">
-        <v>6899.92</v>
+        <v>6509.364</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="17">
@@ -1361,7 +1349,7 @@
       </c>
       <c r="C57" s="14" t="n"/>
       <c r="D57" s="6" t="n">
-        <v>7720.67</v>
+        <v>7283.656</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="17">
@@ -1377,7 +1365,7 @@
       </c>
       <c r="C58" s="14" t="n"/>
       <c r="D58" s="6" t="n">
-        <v>8827.07</v>
+        <v>8327.433000000001</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="17">
@@ -1393,11 +1381,9 @@
       </c>
       <c r="C59" s="14" t="n"/>
       <c r="D59" s="6" t="n">
-        <v>9659.889999999999</v>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61"/>
+        <v>9113.111999999999</v>
+      </c>
+    </row>
     <row r="62" ht="24.75" customHeight="1" s="17">
       <c r="B62" s="20" t="inlineStr">
         <is>
@@ -1405,8 +1391,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64"/>
     <row r="65" ht="18" customHeight="1" s="17">
       <c r="A65" s="7" t="inlineStr">
         <is>
@@ -1438,7 +1422,7 @@
       </c>
       <c r="C66" s="14" t="n"/>
       <c r="D66" s="6" t="n">
-        <v>2698.89</v>
+        <v>2546.123</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="17">
@@ -1454,7 +1438,7 @@
       </c>
       <c r="C67" s="14" t="n"/>
       <c r="D67" s="6" t="n">
-        <v>2722.87</v>
+        <v>2568.745</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="17">
@@ -1470,7 +1454,7 @@
       </c>
       <c r="C68" s="14" t="n"/>
       <c r="D68" s="6" t="n">
-        <v>2949.06</v>
+        <v>2782.138</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="17">
@@ -1486,7 +1470,7 @@
       </c>
       <c r="C69" s="14" t="n"/>
       <c r="D69" s="6" t="n">
-        <v>3130.11</v>
+        <v>2952.936</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="17">
@@ -1502,7 +1486,7 @@
       </c>
       <c r="C70" s="14" t="n"/>
       <c r="D70" s="6" t="n">
-        <v>3359.44</v>
+        <v>3169.283</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="17">
@@ -1518,7 +1502,7 @@
       </c>
       <c r="C71" s="14" t="n"/>
       <c r="D71" s="6" t="n">
-        <v>4031.32</v>
+        <v>3803.139</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="17">
@@ -1534,7 +1518,7 @@
       </c>
       <c r="C72" s="14" t="n"/>
       <c r="D72" s="6" t="n">
-        <v>4417.56</v>
+        <v>4167.513</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="17">
@@ -1550,7 +1534,7 @@
       </c>
       <c r="C73" s="14" t="n"/>
       <c r="D73" s="6" t="n">
-        <v>5564.19</v>
+        <v>5249.243</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="17">
@@ -1566,7 +1550,7 @@
       </c>
       <c r="C74" s="14" t="n"/>
       <c r="D74" s="6" t="n">
-        <v>5849.84</v>
+        <v>5518.721</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="17">
@@ -1582,7 +1566,7 @@
       </c>
       <c r="C75" s="14" t="n"/>
       <c r="D75" s="6" t="n">
-        <v>6670.6</v>
+        <v>6293.02</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="17">
@@ -1598,7 +1582,7 @@
       </c>
       <c r="C76" s="14" t="n"/>
       <c r="D76" s="6" t="n">
-        <v>7213.74</v>
+        <v>6805.421</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="17">
@@ -1614,7 +1598,7 @@
       </c>
       <c r="C77" s="14" t="n"/>
       <c r="D77" s="6" t="n">
-        <v>8135.07</v>
+        <v>7674.599</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" s="17">
@@ -1630,7 +1614,7 @@
       </c>
       <c r="C78" s="14" t="n"/>
       <c r="D78" s="6" t="n">
-        <v>8774.77</v>
+        <v>8278.09</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="17">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="C79" s="14" t="n"/>
       <c r="D79" s="6" t="n">
-        <v>9659.889999999999</v>
+        <v>9113.111999999999</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="17">
@@ -1662,7 +1646,7 @@
       </c>
       <c r="C80" s="14" t="n"/>
       <c r="D80" s="6" t="n">
-        <v>10207.06</v>
+        <v>9629.305</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" s="17">
@@ -1678,7 +1662,7 @@
       </c>
       <c r="C81" s="14" t="n"/>
       <c r="D81" s="6" t="n">
-        <v>11506.58</v>
+        <v>10855.27</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1" s="17">
@@ -1694,7 +1678,7 @@
       </c>
       <c r="C82" s="14" t="n"/>
       <c r="D82" s="6" t="n">
-        <v>12596.88</v>
+        <v>11883.855</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" s="17">
@@ -1710,11 +1694,9 @@
       </c>
       <c r="C83" s="14" t="n"/>
       <c r="D83" s="6" t="n">
-        <v>13518.22</v>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85"/>
+        <v>12753.043</v>
+      </c>
+    </row>
     <row r="86" ht="24.75" customHeight="1" s="17">
       <c r="B86" s="20" t="inlineStr">
         <is>
@@ -1722,8 +1704,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89" ht="18" customHeight="1" s="17">
       <c r="A89" s="7" t="inlineStr">
         <is>
@@ -1755,81 +1735,80 @@
       </c>
       <c r="C90" s="14" t="n"/>
       <c r="D90" s="6" t="n">
-        <v>20478.49</v>
-      </c>
-    </row>
-    <row r="91"/>
+        <v>19319.338</v>
+      </c>
+    </row>
     <row r="93" ht="24.75" customHeight="1" s="17"/>
     <row r="95" ht="18" customHeight="1" s="17"/>
     <row r="96" ht="18" customHeight="1" s="17"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B66:C66"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B89:C89"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B75:C75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
